--- a/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval.xlsx
@@ -456,7 +456,7 @@
         <v>0.1667</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8273</v>
+        <v>0.8817</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1667</v>
+        <v>0.25</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -776,7 +776,7 @@
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -974,16 +974,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7729</v>
+        <v>0.8752</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1012,48 +1012,51 @@
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Prisma is an ORM tool used to simplify database access and management. [...] Prisma Migrate is a database migration tool that facilitates the management of the database schema throughout the application's lifecycle.</t>
+          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>C_05, R_24, R_25</t>
+          <t>R_20, C_03</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>AU_04, AU_07, AU_08</t>
+          <t>AU_02, AU_23, AU_24</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42, 50</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -1064,11 +1067,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.8817</v>
+        <v>0.8881</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1077,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1088,7 +1091,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1097,21 +1100,19 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Traefik is a modern reverse proxy and load balancer designed to manage incoming and outgoing HTTP and HTTPS traffic. [...] HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>C_03, R_20, R_21</t>
+          <t>R_22, C_04</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1126,17 +1127,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
+          <t>CF_M08_C08, *CF_M08_C09</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -1202,17 +1203,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture. [...] In the case of this application, such services run on Amazon EC2 instances and are managed by Docker, which manages the execution of the containers.</t>
+          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_04, C_05, C_07</t>
+          <t>C_07, Scalability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, AU_09</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1222,46 +1223,46 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6433</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Next.js is a framework for building web applications that supports both client-side and server-side rendering. [...] It is used for internationalization (i18n) of applications. It has been used to format messages, dates and numbers in different 'locales' (regional settings), making the application accessible in multiple languages.</t>
+          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_01, R_02, R_16, R_17</t>
+          <t>C_05, Maintainability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_03, AU_06</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42, 73</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7143</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="4">
@@ -1272,17 +1273,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. [...] This approach promotes modularity, code reuse and maintainability, facilitating the management of the application.</t>
+          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_02, R_18, R_19</t>
+          <t>C_06, Adaptability</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_02, AU_15</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1292,11 +1293,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7309</v>
+        <v>0.5961</v>
       </c>
     </row>
     <row r="5">
@@ -1307,7 +1308,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. [...] In the case of this application, it has been used, for example, to manage the PrismaClient instance.</t>
+          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1317,7 +1318,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P_04, AU_08</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1331,7 +1332,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6315</v>
+        <v>0.6387</v>
       </c>
     </row>
   </sheetData>
@@ -1388,22 +1389,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD01</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1411,61 +1412,60 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6758</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
-directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C10</t>
+          <t>*CF_M08_C14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU03</t>
+          <t>CF_M08_AU05</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8217</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
+          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M08_C14</t>
+          <t>*CF_M08_C15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1478,27 +1478,27 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5907</v>
+        <v>0.5822000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1511,27 +1511,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7143</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M08_AD06</t>
+          <t>CF_M08_AD07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
+          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*CF_M08_C16</t>
+          <t>*CF_M08_C17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1540,64 +1540,64 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.66</v>
+        <v>0.7005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*CF_M08_C17</t>
+          <t>*CF_M08_C18, *CF_M08_C19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7013</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M08_AD08</t>
+          <t>CF_M08_AD09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
+          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>*CF_M08_C18, *CF_M08_C19</t>
+          <t>*CF_M08_C20, *CF_M08_C21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1610,60 +1610,60 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6822</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
+          <t>It is designed to simplify access and database management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>*CF_M08_C20, *CF_M08_C21</t>
+          <t>*CF_M08_C22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CF_M08_AU06</t>
+          <t>CF_M08_AU09</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7309</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD10</t>
+          <t>CF_M08_AD11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It is designed to simplify access and database management</t>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C22</t>
+          <t>*CF_M08_C23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.754</v>
+        <v>0.5518999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.7588</v>
+        <v>0.5558999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667</v>
+        <v>0.2143</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8817</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.25</v>
+        <v>0.2611</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1667</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="9">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
-        <v>6</v>
-      </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -752,31 +752,31 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
         <v>12</v>
       </c>
-      <c r="C3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -789,34 +789,34 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -826,25 +826,25 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
         <v>12</v>
       </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -974,25 +974,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M08_AD02</t>
+          <t>CF_M08_AD01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8752</v>
+        <v>0.7565</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1012,135 +1012,218 @@
         <v>3</v>
       </c>
       <c r="L2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Traefik actúa como intermediario para las solicitudes de los clientes a los servidores backend. Redirige las solicitudes entrantes a los servicios internos correspondientes y distribuye el tráfico entre múltiples instancias de un servicio.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Microservices</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>AU_02, AU_05, AU_16</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CF_M08_C08, *CF_M08_C09</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CF_M08_AU03</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CF_M08_AD11</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7727000000000001</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>R_20, C_03</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>AU_02, AU_23, AU_24</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM (Object-Relational Mapping).</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AU_04, AU_07, AU_08, AU_17</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>*CF_M08_C23</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CF_M08_AU09</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CF_M08_AD02</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8889</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>El puerto 80 abre para manejar tráfico HTTP redirigiéndolo al puerto 443 para asegurar que las comunicaciones se realicen de forma segura. El puerto 443 maneja el tráfico HTTPS, estándar para comunicaciones seguras que cifra los datos transmitidos entre los clientes y el servidor, protegiendo la integridad y confidencialidad.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>R_20, R_21, C_03</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>AU_02, AU_05, AU_16, AU_23, AU_24</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
 directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>*CF_M08_C10</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>CF_M08_AU03</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CF_M08_AD01</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8881</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>R_22, C_04</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>AU_02, AU_05</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>CF_M08_C08, *CF_M08_C09</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>CF_M08_AU03</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
+      <c r="U4" t="n">
         <v>43</v>
       </c>
     </row>
@@ -1155,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,27 +1281,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_07, Scalability</t>
+          <t>C_02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03, AU_06, AU_15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1227,112 +1310,287 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6187</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Se conecta a Brevo para crear, enviar y programar correos electrónicos.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_05, Maintainability</t>
+          <t>R_03, R_04, R_05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_03, AU_06, AU_14, AU_18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CF_M08_AD09</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7336</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Observer pattern establishes a one-to-many relationship between objects... When the subject's state changes, it automatically notifies all its observers, allowing them to react appropriately.</t>
+          <t>Utiliza Amazon S3 para almacenar y recuperar archivos.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_06, Adaptability</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_03, AU_06, AU_10, AU_19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M08_AD07</t>
+          <t>CF_M08_AD14</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5961</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Singleton pattern ensures that a class has only one instance and provides a global access point to that instance. It is used generally to manage shared resources, such as configurations, logs or database connections, where having multiple instances could lead to inconsistent states or inefficient use of resources.</t>
+          <t>Integra con Stripe para manejar pagos y suscripciones.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C_04, Robustness</t>
+          <t>R_14, R_15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_03, AU_06, AU_11, AU_20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6136</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Implementa Google Analytics para rastrear y analizar el tráfico del sitio.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_03, AU_06, AU_12, AU_21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M08_AD06</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Utiliza Sentry para rastrear y gestionar errores en la aplicación.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_03, AU_06, AU_13, AU_22</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6098</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C_02</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P_02, AU_15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M08_AD09</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7141999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El patrón Observer establece una relación de uno a muchos entre objetos, donde un objeto conocido como el sujeto mantiene una lista de otros objetos llamados observadores.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C_04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5978</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>El patrón Singleton asegura que una clase tenga solo una instancia y proporciona un punto de acceso global a esa instancia. Se utiliza generalmente para gestionar recursos compartidos [...] se ha empleado, por ejemplo, para gestionar la instancia de PrismaClient</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P_04, AU_08</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CF_M08_AD10</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.6387</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M08_AD13</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7391</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,11 +1670,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8749</v>
+        <v>0.8267</v>
       </c>
     </row>
     <row r="3">
@@ -1445,11 +1703,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.584</v>
+        <v>0.5658</v>
       </c>
     </row>
     <row r="4">
@@ -1478,11 +1736,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.7168</v>
       </c>
     </row>
     <row r="5">
@@ -1511,11 +1769,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.6473</v>
+        <v>0.6203</v>
       </c>
     </row>
     <row r="6">
@@ -1544,11 +1802,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.7005</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="7">
@@ -1577,11 +1835,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6881</v>
+        <v>0.6884</v>
       </c>
     </row>
     <row r="8">
@@ -1610,11 +1868,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7336</v>
+        <v>0.7141999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1647,23 +1905,23 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.653</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1676,44 +1934,77 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.7197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>CF_M08_C06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_12</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7081</v>
       </c>
     </row>
   </sheetData>
